--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6880</v>
+        <v>11980</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9502</v>
+        <v>10096</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2622</v>
+        <v>1884</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6880</v>
+        <v>11980</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9502</v>
+        <v>10738</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2622</v>
+        <v>1242</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6880</v>
+        <v>11052</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9502</v>
+        <v>9441</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2622</v>
+        <v>1611</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8818</v>
+        <v>6615</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9502</v>
+        <v>11393</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-684</v>
+        <v>-4778</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8266</v>
+        <v>6615</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3182</v>
+        <v>-4778</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11992</v>
+        <v>6615</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>544</v>
+        <v>-4778</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9094</v>
+        <v>6615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2354</v>
+        <v>-4778</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11992</v>
+        <v>8996</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>544</v>
+        <v>-2397</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -902,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11992</v>
+        <v>12014</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>544</v>
+        <v>621</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>40</v>
@@ -947,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11992</v>
+        <v>6615</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>544</v>
+        <v>-4778</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11992</v>
+        <v>6615</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>544</v>
+        <v>-4778</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11992</v>
+        <v>6711</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>544</v>
+        <v>-4682</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12476</v>
+        <v>10288</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1028</v>
+        <v>-1105</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,36 +1126,36 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8266</v>
+        <v>6615</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11448</v>
+        <v>8800</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3182</v>
+        <v>-2185</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,36 +1171,36 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11992</v>
+        <v>6615</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11448</v>
+        <v>8800</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>544</v>
+        <v>-2185</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1207,36 +1216,36 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6196</v>
+        <v>6711</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11448</v>
+        <v>8800</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5252</v>
+        <v>-2089</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1252,36 +1261,36 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11992</v>
+        <v>10288</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11448</v>
+        <v>8800</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>544</v>
+        <v>1488</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6880</v>
+        <v>6615</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4568</v>
+        <v>-4778</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>23</v>
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6880</v>
+        <v>6711</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4568</v>
+        <v>-4682</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6886</v>
+        <v>6615</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4562</v>
+        <v>-4778</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1432,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6886</v>
+        <v>6615</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4562</v>
+        <v>-4778</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1477,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8481</v>
+        <v>7495</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2967</v>
+        <v>-3898</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1522,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9922</v>
+        <v>11052</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1526</v>
+        <v>-341</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1567,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6196</v>
+        <v>11980</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-5252</v>
+        <v>587</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1612,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,528 +1631,33 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6880</v>
+        <v>12014</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11448</v>
+        <v>11393</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4568</v>
+        <v>621</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>6880</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-4568</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>6886</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-4562</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>7300</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-4148</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>8233</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-3215</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-4058</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>9530</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-1918</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>6880</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-4568</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>6886</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-4562</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>6886</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-4562</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>8233</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-3215</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>9922</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-1526</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>9922</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>11448</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>-1526</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
